--- a/LubanConfig/MiniTemplate/Datas/生成数据/#战斗型Boss属性表_3导.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/生成数据/#战斗型Boss属性表_3导.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\悠手好闲\铁头工作室\方块项目设计案\《冲王》数值_cursor\LubanConfig\MiniTemplate\Datas\生成数据\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\悠手好闲\铁头工作室\方块项目设计案\《冲王》数值_cursor\新数据生成\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="战斗型Boss属性" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="51">
   <si>
     <t>##var</t>
   </si>
@@ -105,6 +105,9 @@
     <t>##</t>
   </si>
   <si>
+    <t>普通坦克 1</t>
+  </si>
+  <si>
     <t>普通</t>
   </si>
   <si>
@@ -117,13 +120,16 @@
     <t>森林,草原,雪山</t>
   </si>
   <si>
+    <t>萨哈比精英坦克 1</t>
+  </si>
+  <si>
     <t>精英</t>
   </si>
   <si>
     <t>萨哈比精英坦克</t>
   </si>
   <si>
-    <t>森林</t>
+    <t>泰森 1</t>
   </si>
   <si>
     <t>近战</t>
@@ -132,7 +138,7 @@
     <t>泰森</t>
   </si>
   <si>
-    <t>雪山</t>
+    <t>残酷射手 1</t>
   </si>
   <si>
     <t>远程</t>
@@ -141,23 +147,31 @@
     <t>残酷射手</t>
   </si>
   <si>
-    <t>草原</t>
-  </si>
-  <si>
-    <t>战斗普通Boss</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>战斗精英坦克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>战斗泰森Boss</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>战斗射手Boss</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>刘易斯 1</t>
+  </si>
+  <si>
+    <t>刘易斯</t>
+  </si>
+  <si>
+    <t>精射手 1</t>
+  </si>
+  <si>
+    <t>精射手</t>
+  </si>
+  <si>
+    <t>垃圾刺客 1</t>
+  </si>
+  <si>
+    <t>刺客</t>
+  </si>
+  <si>
+    <t>垃圾刺客</t>
+  </si>
+  <si>
+    <t>影流之主 1</t>
+  </si>
+  <si>
+    <t>影流之主</t>
   </si>
 </sst>
 </file>
@@ -552,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="24.25" customWidth="1"/>
@@ -788,7 +802,7 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.15">
       <c r="B4" s="2" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2">
         <v>3001</v>
@@ -815,7 +829,7 @@
         <v>5.6</v>
       </c>
       <c r="K4" s="2">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="L4" s="2">
         <v>0</v>
@@ -824,22 +838,22 @@
         <v>196.4</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q4" s="2">
-        <v>16.367000000000001</v>
+        <v>1.6367</v>
       </c>
       <c r="R4" s="2">
-        <v>4.9100999999999999</v>
+        <v>1.6367</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T4" s="2">
         <v>20</v>
@@ -856,7 +870,7 @@
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.15">
       <c r="B5" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C5" s="2">
         <v>3002</v>
@@ -883,7 +897,7 @@
         <v>6.3209999999999997</v>
       </c>
       <c r="K5" s="2">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="L5" s="2">
         <v>0</v>
@@ -892,22 +906,22 @@
         <v>294.74700000000001</v>
       </c>
       <c r="N5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>1.6367</v>
+      </c>
+      <c r="R5" s="2">
+        <v>1.6367</v>
+      </c>
+      <c r="S5" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q5" s="2">
-        <v>16.367000000000001</v>
-      </c>
-      <c r="R5" s="2">
-        <v>4.9100999999999999</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="T5" s="2">
         <v>20</v>
@@ -924,7 +938,7 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.15">
       <c r="B6" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C6" s="2">
         <v>3003</v>
@@ -960,22 +974,22 @@
         <v>196.3</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q6" s="2">
-        <v>16.367000000000001</v>
+        <v>1.6367</v>
       </c>
       <c r="R6" s="2">
-        <v>4.9100999999999999</v>
+        <v>1.6367</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="T6" s="2">
         <v>20</v>
@@ -992,7 +1006,7 @@
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.15">
       <c r="B7" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C7" s="2">
         <v>3004</v>
@@ -1028,22 +1042,22 @@
         <v>196.9</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q7" s="2">
-        <v>16.367000000000001</v>
+        <v>1.6367</v>
       </c>
       <c r="R7" s="2">
-        <v>4.9100999999999999</v>
+        <v>1.6367</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T7" s="2">
         <v>20</v>
@@ -1055,12 +1069,283 @@
         <v>10</v>
       </c>
       <c r="W7" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="B8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="2">
+        <v>3005</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1200</v>
+      </c>
+      <c r="F8" s="2">
+        <v>33.6</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2">
+        <v>11.2</v>
+      </c>
+      <c r="K8" s="2">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2">
+        <v>198.4</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>1.6367</v>
+      </c>
+      <c r="R8" s="2">
+        <v>1.6367</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="T8" s="2">
+        <v>20</v>
+      </c>
+      <c r="U8" s="2">
+        <v>0.67310000000000003</v>
+      </c>
+      <c r="V8" s="2">
+        <v>10</v>
+      </c>
+      <c r="W8" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="B9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="2">
+        <v>3006</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <v>900</v>
+      </c>
+      <c r="F9" s="2">
+        <v>48</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2">
+        <v>3</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2">
+        <v>20.8</v>
+      </c>
+      <c r="K9" s="2">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2">
+        <v>235.6</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>1.6367</v>
+      </c>
+      <c r="R9" s="2">
+        <v>1.6367</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="T9" s="2">
+        <v>20</v>
+      </c>
+      <c r="U9" s="2">
+        <v>0.79930000000000001</v>
+      </c>
+      <c r="V9" s="2">
+        <v>10</v>
+      </c>
+      <c r="W9" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="B10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3007</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
+        <v>700</v>
+      </c>
+      <c r="F10" s="2">
+        <v>45</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2">
+        <v>2</v>
+      </c>
+      <c r="J10" s="2">
+        <v>15</v>
+      </c>
+      <c r="K10" s="2">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2">
+        <v>175</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>1.6367</v>
+      </c>
+      <c r="R10" s="2">
+        <v>1.6367</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="T10" s="2">
+        <v>20</v>
+      </c>
+      <c r="U10" s="2">
+        <v>0.59370000000000001</v>
+      </c>
+      <c r="V10" s="2">
+        <v>10</v>
+      </c>
+      <c r="W10" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="B11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="2">
+        <v>3008</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>900</v>
+      </c>
+      <c r="F11" s="2">
+        <v>48</v>
+      </c>
+      <c r="G11" s="2">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J11" s="2">
+        <v>16</v>
+      </c>
+      <c r="K11" s="2">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2">
+        <v>202</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>1.6367</v>
+      </c>
+      <c r="R11" s="2">
+        <v>1.6367</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="T11" s="2">
+        <v>20</v>
+      </c>
+      <c r="U11" s="2">
+        <v>1.028</v>
+      </c>
+      <c r="V11" s="2">
+        <v>10</v>
+      </c>
+      <c r="W11" s="2">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>